--- a/questionnaire_templates/010_remote_work_conditions_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/010_remote_work_conditions_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -643,21 +643,17 @@
           <t>Feedback and Comments</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Please provide your feedback on our remote work conditions questionnaire.</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -673,7 +669,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -696,7 +692,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -719,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -742,7 +738,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -765,329 +761,30 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>collaboration_3</t>
+          <t>communication_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Collaboration and Teamwork 2</t>
+          <t>Communication 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>communication_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Communication 2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>productivity_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Productivity 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>well_being_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Well Being 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>feedback_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Feedback and Comments 2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>collaboration_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Collaboration and Teamwork 3</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>communication_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Communication 3</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>productivity_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Productivity 3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>well_being_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Well Being 3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>feedback_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Feedback and Comments 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>collaboration_5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Collaboration and Teamwork 4</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>communication_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Communication 4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>productivity_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Productivity 4</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>well_being_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Well Being 4</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,680 +827,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>work_arrangement_choices</t>
+          <t>setup_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>provided</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Provided</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>work_arrangement_choices</t>
+          <t>setup_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_provided</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Provided</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>collaboration_choices</t>
+          <t>work_arrangement_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>conducive</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Conducive</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>collaboration_choices</t>
+          <t>work_arrangement_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_conducive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Conducive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>productivity_choices</t>
+          <t>collaboration_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>productivity_choices</t>
+          <t>collaboration_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>well_being_choices</t>
+          <t>collaboration_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>well_being_choices</t>
+          <t>productivity_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>collaboration_2_choices</t>
+          <t>productivity_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>collaboration_2_choices</t>
+          <t>productivity_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>well_being_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>well_being_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>productivity_2_choices</t>
+          <t>well_being_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>productivity_2_choices</t>
+          <t>collaboration_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>well_being_2_choices</t>
+          <t>collaboration_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>well_being_2_choices</t>
+          <t>collaboration_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>collaboration_3_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>collaboration_3_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>communication_2_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>communication_2_choices</t>
+          <t>productivity_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>productivity_3_choices</t>
+          <t>productivity_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>productivity_3_choices</t>
+          <t>productivity_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>well_being_3_choices</t>
+          <t>well_being_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>well_being_3_choices</t>
+          <t>well_being_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>collaboration_4_choices</t>
+          <t>well_being_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>collaboration_4_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>communication_3_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>communication_3_choices</t>
+          <t>communication_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>productivity_4_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>productivity_4_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>well_being_4_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>well_being_4_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>collaboration_5_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>collaboration_5_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>communication_4_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>communication_4_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>productivity_5_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>productivity_5_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>well_being_5_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>well_being_5_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
